--- a/samples/calibration01/stereo_calib2.xlsx
+++ b/samples/calibration01/stereo_calib2.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
